--- a/엄정숙.xlsx
+++ b/엄정숙.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2348A537-B8F9-45A9-A16F-83F362057E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A47760-AD80-467C-83EE-38B60F23A049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
   <si>
     <t>교시</t>
   </si>
@@ -76,13 +76,17 @@
   </si>
   <si>
     <t>통사2</t>
+  </si>
+  <si>
+    <t>동아리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +107,13 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -180,7 +191,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -206,6 +217,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -673,7 +687,9 @@
       <c r="E10" s="2">
         <v>104</v>
       </c>
-      <c r="F10" s="5"/>
+      <c r="F10" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
@@ -699,7 +715,9 @@
         <v>105</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="F12" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8"/>
@@ -747,12 +765,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="A14:A15"/>
@@ -761,16 +783,12 @@
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F10:F11"/>
   </mergeCells>
